--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>113.1346826508097</v>
+        <v>18.38438593075657</v>
       </c>
       <c r="D2" t="n">
-        <v>113.1135126291571</v>
+        <v>18.38094580223802</v>
       </c>
       <c r="E2" t="n">
-        <v>41.60137954762705</v>
+        <v>6.760224176489396</v>
       </c>
       <c r="F2" t="n">
-        <v>41.58685943330804</v>
+        <v>6.757864657912556</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>102.410337170507</v>
+        <v>16.64167979020738</v>
       </c>
       <c r="D3" t="n">
-        <v>102.2621510755132</v>
+        <v>16.6175995497709</v>
       </c>
       <c r="E3" t="n">
-        <v>41.60137954762705</v>
+        <v>6.760224176489396</v>
       </c>
       <c r="F3" t="n">
-        <v>41.58685943330804</v>
+        <v>6.757864657912556</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>74.94826698581336</v>
+        <v>12.17909338519467</v>
       </c>
       <c r="D4" t="n">
-        <v>74.92618361304794</v>
+        <v>12.17550483712029</v>
       </c>
       <c r="E4" t="n">
-        <v>41.60137954762705</v>
+        <v>6.760224176489396</v>
       </c>
       <c r="F4" t="n">
-        <v>41.58685943330804</v>
+        <v>6.757864657912556</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.01359805005795</v>
+        <v>1.952209683134418</v>
       </c>
       <c r="D5" t="n">
-        <v>11.86518603601373</v>
+        <v>1.928092730852231</v>
       </c>
       <c r="E5" t="n">
-        <v>41.60137954762705</v>
+        <v>6.760224176489396</v>
       </c>
       <c r="F5" t="n">
-        <v>41.58685943330804</v>
+        <v>6.757864657912556</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.92579092957071</v>
+        <v>3.23794102605524</v>
       </c>
       <c r="D6" t="n">
-        <v>20.01436097129432</v>
+        <v>3.252333657835326</v>
       </c>
       <c r="E6" t="n">
-        <v>41.60137954762705</v>
+        <v>6.760224176489396</v>
       </c>
       <c r="F6" t="n">
-        <v>41.58685943330804</v>
+        <v>6.757864657912556</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
